--- a/2025-MLS-projections/USA Catch/USA_Catch.xlsx
+++ b/2025-MLS-projections/USA Catch/USA_Catch.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jon.brodziak\Desktop\2024 WCNPO MLS Rebuilding\2025 MLS projections\USA Catch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370C2242-7A0A-4279-B31F-AFFCC894C981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A21BE4-1E3B-4107-8404-B7F460283CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{B7E737E3-9C19-4BAF-A933-783AA9D546EB}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8863" firstSheet="1" activeTab="1" xr2:uid="{B7E737E3-9C19-4BAF-A933-783AA9D546EB}"/>
   </bookViews>
   <sheets>
     <sheet name="US WCNPO MLS Catch" sheetId="6" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="149">
   <si>
     <t>report_year</t>
   </si>
@@ -315,9 +315,6 @@
     <t>PRELIMINARY</t>
   </si>
   <si>
-    <t>WCPFC 2024 YEARBOOK WCNPO MLS CATCH BIOMASS (MT)</t>
-  </si>
-  <si>
     <t>YEAR</t>
   </si>
   <si>
@@ -375,18 +372,12 @@
     <t>VU</t>
   </si>
   <si>
-    <t>American Samoa LL</t>
-  </si>
-  <si>
     <t>F16</t>
   </si>
   <si>
     <t>US</t>
   </si>
   <si>
-    <t>G8 + AmSam LL</t>
-  </si>
-  <si>
     <t>F17</t>
   </si>
   <si>
@@ -450,12 +441,6 @@
     <t>Mean Weight (kg)</t>
   </si>
   <si>
-    <t>MLS Catch Biomass (mt)</t>
-  </si>
-  <si>
-    <t>MLS Mean Weight (kg)</t>
-  </si>
-  <si>
     <t>sold_est_kgs</t>
   </si>
   <si>
@@ -474,9 +459,6 @@
     <t>WCPFC-North US-HW Yearbook Catch</t>
   </si>
   <si>
-    <t>HDAR Catch</t>
-  </si>
-  <si>
     <t>Dealer Sold</t>
   </si>
   <si>
@@ -496,6 +478,39 @@
   </si>
   <si>
     <t>WCPFC-North US Yearbook Total Catch (mt)</t>
+  </si>
+  <si>
+    <t>USA Hawaii Longline MLS Mean Weight (kg)</t>
+  </si>
+  <si>
+    <t>USA Hawaii Longline MLS Catch Biomass (mt)</t>
+  </si>
+  <si>
+    <t>HDAR Non-Longline Catch</t>
+  </si>
+  <si>
+    <t>USA Non-Longline MLS Catch Biomass (mt)</t>
+  </si>
+  <si>
+    <t>USA Non-Longline MLS Mean Weight (kg)</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>WCNPO MLS Catch Biomass (mt) from WCPFC 2024 Yearbook</t>
+  </si>
+  <si>
+    <t>Fleet Group</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>American Samoa LL*</t>
+  </si>
+  <si>
+    <t>G8 + AmSam LL*</t>
   </si>
 </sst>
 </file>
@@ -564,7 +579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -653,13 +668,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -690,12 +793,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -752,6 +849,159 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1118,7 +1368,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -1130,101 +1380,101 @@
       <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="25">
+      <c r="A3" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="23">
         <v>2020</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="24">
         <v>2021</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="24">
         <v>2022</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="24">
         <v>2023</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="24">
         <v>2024</v>
       </c>
-      <c r="G3" s="29" t="s">
-        <v>141</v>
+      <c r="G3" s="27" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="22">
+      <c r="A4" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="20">
         <v>323.03758445389201</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="20">
         <v>256.49358231668299</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <v>288.540794295973</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="20">
         <v>207.28263460981</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="20">
         <v>565.12376371508105</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="31">
         <f>AVERAGE(B4:F4)</f>
         <v>328.09567187828782</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="23">
+      <c r="A5" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="21">
         <v>9.9789999999999992</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="21">
         <v>8.82</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="21">
         <v>9.5850000000000009</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="21">
         <v>6.7430000000000003</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="21">
         <v>18.591000000000001</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="32">
         <f t="shared" ref="G5:G10" si="0">AVERAGE(B5:F5)</f>
         <v>10.743600000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="40">
+      <c r="A6" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="38">
         <f>B4+B5</f>
         <v>333.01658445389199</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="38">
         <f>C4+C5</f>
         <v>265.31358231668298</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="38">
         <f>D4+D5</f>
         <v>298.12579429597298</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="38">
         <f>E4+E5</f>
         <v>214.02563460981</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="38">
         <f>F4+F5</f>
         <v>583.71476371508106</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="39">
         <f t="shared" si="0"/>
         <v>338.83927187828783</v>
       </c>
@@ -1237,85 +1487,85 @@
       <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="25">
         <v>250</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="25">
         <v>207</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="25">
         <v>239</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="25">
         <v>175</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="25">
         <v>175</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="31">
         <f t="shared" si="0"/>
         <v>209.2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="28">
+      <c r="A9" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="26">
         <v>47</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="26">
         <v>30</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="26">
         <v>25</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="26">
         <v>13</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="26">
         <v>13</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="32">
         <f t="shared" si="0"/>
         <v>25.6</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="B10" s="25">
+      <c r="A10" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B10" s="23">
         <f>SUM(B8:B9)</f>
         <v>297</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="23">
         <f>SUM(C8:C9)</f>
         <v>237</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="23">
         <f t="shared" ref="D10:F10" si="1">SUM(D8:D9)</f>
         <v>264</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="23">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="23">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="36">
         <f t="shared" si="0"/>
         <v>234.8</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -1327,85 +1577,85 @@
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="25">
+      <c r="A16" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="23">
         <v>2020</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="24">
         <v>2021</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="24">
         <v>2022</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="24">
         <v>2023</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="24">
         <v>2024</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>141</v>
+      <c r="G16" s="35" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="22">
+      <c r="A17" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="20">
         <v>29.863879490976426</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="20">
         <v>28.703399990676253</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <v>27.90260074421942</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="20">
         <v>31.473221167599451</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="20">
         <v>24.196085105115646</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="31">
         <f t="shared" ref="G17:G18" si="2">AVERAGE(B17:F17)</f>
         <v>28.427837299717435</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="24">
+      <c r="A18" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="22">
         <v>33.374581939799334</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="22">
         <v>36.75</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="22">
         <v>31.120129870129869</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="22">
         <v>32.109523809523807</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="22">
         <v>25.965083798882681</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="33">
         <f t="shared" si="2"/>
         <v>31.863863883667136</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB0545D-5FD6-476F-AA31-3EC8815FAC30}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15" style="2" bestFit="1" customWidth="1"/>
@@ -1434,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>9</v>
@@ -1443,7 +1693,7 @@
         <v>10</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>11</v>
@@ -1603,135 +1853,174 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
+      <c r="D7" s="17" cm="1">
+        <f t="array" ref="D7:H7">TRANSPOSE(G2:G6)</f>
+        <v>323037.58445389202</v>
+      </c>
+      <c r="E7" s="17">
+        <v>256493.58231668299</v>
+      </c>
+      <c r="F7" s="17">
+        <v>288540.79429597303</v>
+      </c>
+      <c r="G7" s="17">
+        <v>207282.63460980999</v>
+      </c>
+      <c r="H7" s="17">
+        <v>565123.76371508103</v>
+      </c>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D9" s="17">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D9" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D10" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="48"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D11" s="40">
         <v>2020</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E11" s="44">
         <v>2021</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F11" s="41">
         <v>2022</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G11" s="45">
         <v>2023</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H11" s="43">
         <v>2024</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D10" s="16">
-        <f>D11/1000</f>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D12" s="78">
+        <f>D7/1000</f>
         <v>323.03758445389201</v>
       </c>
-      <c r="E10" s="16">
-        <f>E11/1000</f>
+      <c r="E12" s="79">
+        <f>E7/1000</f>
         <v>256.49358231668299</v>
       </c>
-      <c r="F10" s="16">
-        <f t="shared" ref="F10:H10" si="1">F11/1000</f>
+      <c r="F12" s="80">
+        <f>F7/1000</f>
         <v>288.540794295973</v>
       </c>
-      <c r="G10" s="16">
-        <f t="shared" si="1"/>
+      <c r="G12" s="79">
+        <f>G7/1000</f>
         <v>207.28263460981</v>
       </c>
-      <c r="H10" s="16">
-        <f t="shared" si="1"/>
+      <c r="H12" s="81">
+        <f>H7/1000</f>
         <v>565.12376371508105</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D11" s="19" cm="1">
-        <f t="array" ref="D11:H11">TRANSPOSE(G2:G6)</f>
-        <v>323037.58445389202</v>
-      </c>
-      <c r="E11" s="19">
-        <v>256493.58231668299</v>
-      </c>
-      <c r="F11" s="19">
-        <v>288540.79429597303</v>
-      </c>
-      <c r="G11" s="19">
-        <v>207282.63460980999</v>
-      </c>
-      <c r="H11" s="19">
-        <v>565123.76371508103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="E13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" s="2"/>
-    </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D14" s="17">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D15" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D16" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="48"/>
+    </row>
+    <row r="17" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D17" s="49">
         <v>2020</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E17" s="50">
         <v>2021</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F17" s="51">
         <v>2022</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G17" s="52">
         <v>2023</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H17" s="53">
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="D15" s="16" cm="1">
-        <f t="array" ref="D15:H15">TRANSPOSE(H2:H6)</f>
+    <row r="18" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D18" s="82" cm="1">
+        <f t="array" ref="D18:H18">TRANSPOSE(H2:H6)</f>
         <v>29.863879490976426</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E18" s="83">
         <v>28.703399990676253</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F18" s="84">
         <v>27.90260074421942</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G18" s="83">
         <v>31.473221167599451</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H18" s="85">
         <v>24.196085105115646</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <mergeCells count="4">
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D15:H15"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFD7D5C-84CC-4206-98E0-10275D4D569C}">
-  <dimension ref="A1:K16"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.921875" customWidth="1"/>
-    <col min="3" max="3" width="9.07421875" customWidth="1"/>
+    <col min="1" max="1" width="23.3828125" customWidth="1"/>
+    <col min="3" max="3" width="14.53515625" customWidth="1"/>
     <col min="7" max="7" width="12.84375" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="13.53515625" customWidth="1"/>
+    <col min="10" max="10" width="14.4609375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.4">
@@ -1748,25 +2037,25 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" t="s">
         <v>133</v>
       </c>
-      <c r="F1" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" t="s">
-        <v>139</v>
-      </c>
       <c r="H1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
@@ -1803,7 +2092,7 @@
       <c r="J2">
         <v>299</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="18">
         <f>D2/J2</f>
         <v>33.374581939799334</v>
       </c>
@@ -1842,7 +2131,7 @@
       <c r="J3">
         <v>240</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="18">
         <f t="shared" ref="K3:K6" si="2">D3/J3</f>
         <v>36.75</v>
       </c>
@@ -1881,7 +2170,7 @@
       <c r="J4">
         <v>308</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="18">
         <f t="shared" si="2"/>
         <v>31.120129870129869</v>
       </c>
@@ -1920,7 +2209,7 @@
       <c r="J5">
         <v>210</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="18">
         <f t="shared" si="2"/>
         <v>32.109523809523807</v>
       </c>
@@ -1959,1132 +2248,1204 @@
       <c r="J6">
         <v>716</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="18">
         <f t="shared" si="2"/>
         <v>25.965083798882681</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="73"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="55"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="57"/>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B9" s="17">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="73"/>
+      <c r="B9" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="15"/>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="41">
         <v>2020</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C10" s="41">
         <v>2021</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D10" s="41">
         <v>2022</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E10" s="42">
         <v>2023</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F10" s="43">
         <v>2024</v>
       </c>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B10" s="10">
-        <f t="array" ref="B10:F10">TRANSPOSE(E2:E6)</f>
+      <c r="G10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A11" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="68">
+        <f t="array" ref="B11:F11">TRANSPOSE(E2:E6)</f>
         <v>9.9789999999999992</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C11" s="69">
         <v>8.82</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D11" s="69">
         <v>9.5850000000000009</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E11" s="69">
         <v>6.7430000000000003</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F11" s="70">
         <v>18.591000000000001</v>
       </c>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="10">
-        <f t="array" ref="B11:F11">TRANSPOSE(G2:G6)</f>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A12" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" s="65">
+        <f t="array" ref="B12:F12">TRANSPOSE(G2:G6)</f>
         <v>6.351</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C12" s="21">
         <v>5.1269999999999998</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D12" s="21">
         <v>7.1840000000000002</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E12" s="21">
         <v>5.577</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F12" s="62">
         <v>7.3410000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="10">
-        <f t="array" ref="B12:F12">TRANSPOSE(I2:I6)</f>
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="66">
+        <f t="array" ref="B13:F13">TRANSPOSE(I2:I6)</f>
         <v>7.8310000000000004</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C13" s="22">
         <v>6.3520000000000003</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D13" s="22">
         <v>8.7910000000000004</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E13" s="22">
         <v>6.8079999999999998</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F13" s="64">
         <v>8.8339999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B15" s="17">
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="73"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="15"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="73"/>
+      <c r="B16" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="72">
         <v>2020</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C17" s="59">
         <v>2021</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D17" s="59">
         <v>2022</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E17" s="60">
         <v>2023</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F17" s="61">
         <v>2024</v>
       </c>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="10">
-        <f t="array" ref="B16:F16">TRANSPOSE(K2:K6)</f>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="74">
+        <f t="array" ref="B18:F18">TRANSPOSE(K2:K6)</f>
         <v>33.374581939799334</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C18" s="75">
         <v>36.75</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D18" s="75">
         <v>31.120129870129869</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E18" s="75">
         <v>32.109523809523807</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F18" s="76">
         <v>25.965083798882681</v>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G18" s="19"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B16:F16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="84" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFA2452-B24B-4CE1-9BFD-E03807491D72}">
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AD67"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.765625" customWidth="1"/>
+    <col min="1" max="1" width="17.15234375" customWidth="1"/>
     <col min="2" max="2" width="10.84375" customWidth="1"/>
     <col min="4" max="4" width="10.69140625" customWidth="1"/>
-    <col min="6" max="6" width="19.61328125" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
-    <col min="8" max="8" width="9.53515625" customWidth="1"/>
-    <col min="9" max="9" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.61328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.69140625" customWidth="1"/>
-    <col min="13" max="13" width="6.84375" customWidth="1"/>
-    <col min="15" max="15" width="6.07421875" customWidth="1"/>
-    <col min="16" max="16" width="10.4609375" customWidth="1"/>
-    <col min="18" max="18" width="3.3828125" customWidth="1"/>
-    <col min="19" max="19" width="7.61328125" customWidth="1"/>
-    <col min="24" max="24" width="4.3828125" customWidth="1"/>
-    <col min="25" max="25" width="7.53515625" customWidth="1"/>
+    <col min="7" max="7" width="21.3046875" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="9.53515625" customWidth="1"/>
+    <col min="10" max="10" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.61328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.69140625" customWidth="1"/>
+    <col min="14" max="14" width="6.84375" customWidth="1"/>
+    <col min="16" max="16" width="6.07421875" customWidth="1"/>
+    <col min="17" max="17" width="10.4609375" customWidth="1"/>
+    <col min="19" max="19" width="3.3828125" customWidth="1"/>
+    <col min="20" max="20" width="7.61328125" customWidth="1"/>
+    <col min="25" max="25" width="4.3828125" customWidth="1"/>
+    <col min="26" max="26" width="7.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:30" ht="21" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="87"/>
+    </row>
+    <row r="3" spans="1:30" ht="29.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="96" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="25">
+        <v>2021</v>
+      </c>
+      <c r="C3" s="25">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="25">
+        <v>2023</v>
+      </c>
+      <c r="E3" s="86">
+        <v>2024</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="I3" t="s">
         <v>85</v>
       </c>
-      <c r="B3">
+      <c r="J3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" t="s">
+        <v>88</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" t="s">
+        <v>86</v>
+      </c>
+      <c r="W3" t="s">
+        <v>87</v>
+      </c>
+      <c r="X3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A4" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="25">
+        <v>139</v>
+      </c>
+      <c r="C4" s="25">
+        <v>100</v>
+      </c>
+      <c r="D4" s="25">
+        <v>89</v>
+      </c>
+      <c r="E4" s="86">
+        <v>89</v>
+      </c>
+      <c r="F4" s="31">
+        <f>AVERAGE(B4:E4)</f>
+        <v>104.25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4">
+        <v>2020</v>
+      </c>
+      <c r="K4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="N4" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" t="s">
+        <v>90</v>
+      </c>
+      <c r="P4">
         <v>2021</v>
       </c>
-      <c r="C3">
+      <c r="Q4" t="s">
+        <v>91</v>
+      </c>
+      <c r="R4">
+        <v>15</v>
+      </c>
+      <c r="T4" t="s">
+        <v>89</v>
+      </c>
+      <c r="U4" t="s">
+        <v>90</v>
+      </c>
+      <c r="V4">
         <v>2022</v>
       </c>
-      <c r="D3">
+      <c r="W4" t="s">
+        <v>91</v>
+      </c>
+      <c r="X4">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB4">
         <v>2023</v>
       </c>
-      <c r="E3">
-        <v>2024</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="AC4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A5" s="94" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="87">
+        <v>207</v>
+      </c>
+      <c r="C5" s="87">
+        <v>239</v>
+      </c>
+      <c r="D5" s="87">
+        <v>175</v>
+      </c>
+      <c r="E5" s="88">
+        <v>175</v>
+      </c>
+      <c r="F5" s="32">
+        <f t="shared" ref="F5:F8" si="0">AVERAGE(B5:E5)</f>
+        <v>199</v>
+      </c>
+      <c r="H5" t="s">
         <v>89</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="N3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O3" t="s">
-        <v>87</v>
-      </c>
-      <c r="P3" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="I5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5">
+        <v>2020</v>
+      </c>
+      <c r="K5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
         <v>89</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="T3" t="s">
-        <v>86</v>
-      </c>
-      <c r="U3" t="s">
-        <v>87</v>
-      </c>
-      <c r="V3" t="s">
-        <v>88</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="O5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P5">
+        <v>2021</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>94</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="T5" t="s">
         <v>89</v>
       </c>
-      <c r="Y3" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="U5" t="s">
+        <v>90</v>
+      </c>
+      <c r="V5">
+        <v>2022</v>
+      </c>
+      <c r="W5" t="s">
+        <v>94</v>
+      </c>
+      <c r="X5">
+        <v>9</v>
+      </c>
+      <c r="Z5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="AA5" t="s">
         <v>90</v>
       </c>
-      <c r="B4">
-        <v>139</v>
-      </c>
-      <c r="C4">
+      <c r="AB5">
+        <v>2023</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A6" s="94" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="87">
+        <v>249</v>
+      </c>
+      <c r="C6" s="87">
+        <v>284</v>
+      </c>
+      <c r="D6" s="87">
+        <v>461</v>
+      </c>
+      <c r="E6" s="88">
+        <v>461</v>
+      </c>
+      <c r="F6" s="32">
+        <f t="shared" si="0"/>
+        <v>363.75</v>
+      </c>
+      <c r="H6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6">
+        <v>2020</v>
+      </c>
+      <c r="K6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>89</v>
+      </c>
+      <c r="O6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6">
+        <v>2021</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>96</v>
+      </c>
+      <c r="R6">
+        <v>60</v>
+      </c>
+      <c r="T6" t="s">
+        <v>89</v>
+      </c>
+      <c r="U6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V6">
+        <v>2022</v>
+      </c>
+      <c r="W6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X6">
+        <v>39</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB6">
+        <v>2023</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="89">
+        <v>1091</v>
+      </c>
+      <c r="C7" s="89">
+        <v>804</v>
+      </c>
+      <c r="D7" s="89">
+        <v>836</v>
+      </c>
+      <c r="E7" s="90">
+        <v>836</v>
+      </c>
+      <c r="F7" s="33">
+        <f t="shared" si="0"/>
+        <v>891.75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7">
+        <v>2020</v>
+      </c>
+      <c r="K7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>89</v>
+      </c>
+      <c r="O7" t="s">
+        <v>90</v>
+      </c>
+      <c r="P7">
+        <v>2021</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>98</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+      <c r="T7" t="s">
+        <v>89</v>
+      </c>
+      <c r="U7" t="s">
+        <v>90</v>
+      </c>
+      <c r="V7">
+        <v>2022</v>
+      </c>
+      <c r="W7" t="s">
+        <v>98</v>
+      </c>
+      <c r="X7">
+        <v>12</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB7">
+        <v>2023</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="89">
+        <v>1686</v>
+      </c>
+      <c r="C8" s="89">
+        <v>1427</v>
+      </c>
+      <c r="D8" s="89">
+        <v>1561</v>
+      </c>
+      <c r="E8" s="90">
+        <v>1561</v>
+      </c>
+      <c r="F8" s="33">
+        <f t="shared" si="0"/>
+        <v>1558.75</v>
+      </c>
+      <c r="H8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8">
+        <v>2020</v>
+      </c>
+      <c r="K8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O8" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8">
+        <v>2021</v>
+      </c>
+      <c r="Q8" t="s">
         <v>100</v>
       </c>
-      <c r="D4">
+      <c r="R8">
+        <v>6</v>
+      </c>
+      <c r="T8" t="s">
         <v>89</v>
       </c>
-      <c r="E4">
+      <c r="U8" t="s">
+        <v>90</v>
+      </c>
+      <c r="V8">
+        <v>2022</v>
+      </c>
+      <c r="W8" t="s">
+        <v>100</v>
+      </c>
+      <c r="X8">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="s">
         <v>89</v>
       </c>
-      <c r="G4" t="s">
+      <c r="AA8" t="s">
         <v>90</v>
       </c>
-      <c r="H4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4">
+      <c r="AB8">
+        <v>2023</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A9" s="87"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="H9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J9">
         <v>2020</v>
       </c>
-      <c r="J4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K4">
-        <v>50</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="K9" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9">
+        <v>6</v>
+      </c>
+      <c r="N9" t="s">
+        <v>89</v>
+      </c>
+      <c r="O9" t="s">
         <v>90</v>
       </c>
-      <c r="N4" t="s">
-        <v>91</v>
-      </c>
-      <c r="O4">
+      <c r="P9">
         <v>2021</v>
       </c>
-      <c r="P4" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q4">
-        <v>15</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="Q9" t="s">
+        <v>101</v>
+      </c>
+      <c r="R9">
+        <v>52</v>
+      </c>
+      <c r="T9" t="s">
+        <v>89</v>
+      </c>
+      <c r="U9" t="s">
         <v>90</v>
       </c>
-      <c r="T4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U4">
+      <c r="V9">
         <v>2022</v>
       </c>
-      <c r="V4" t="s">
-        <v>92</v>
-      </c>
-      <c r="W4">
-        <v>11</v>
-      </c>
-      <c r="Y4" t="s">
+      <c r="W9" t="s">
+        <v>101</v>
+      </c>
+      <c r="X9">
+        <v>27</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA9" t="s">
         <v>90</v>
       </c>
-      <c r="Z4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA4">
+      <c r="AB9">
         <v>2023</v>
       </c>
-      <c r="AB4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5">
-        <v>207</v>
-      </c>
-      <c r="C5">
-        <v>239</v>
-      </c>
-      <c r="D5">
-        <v>175</v>
-      </c>
-      <c r="E5">
-        <v>175</v>
-      </c>
-      <c r="G5" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5">
-        <v>2020</v>
-      </c>
-      <c r="J5" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5">
+      <c r="AC9" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD9">
         <v>1</v>
       </c>
-      <c r="M5" t="s">
-        <v>90</v>
-      </c>
-      <c r="N5" t="s">
-        <v>91</v>
-      </c>
-      <c r="O5">
-        <v>2021</v>
-      </c>
-      <c r="P5" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="S5" t="s">
-        <v>90</v>
-      </c>
-      <c r="T5" t="s">
-        <v>91</v>
-      </c>
-      <c r="U5">
-        <v>2022</v>
-      </c>
-      <c r="V5" t="s">
-        <v>95</v>
-      </c>
-      <c r="W5">
-        <v>9</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA5">
-        <v>2023</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6">
-        <v>249</v>
-      </c>
-      <c r="C6">
-        <v>284</v>
-      </c>
-      <c r="D6">
-        <v>461</v>
-      </c>
-      <c r="E6">
-        <v>461</v>
-      </c>
-      <c r="G6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6">
-        <v>2020</v>
-      </c>
-      <c r="J6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>90</v>
-      </c>
-      <c r="N6" t="s">
-        <v>91</v>
-      </c>
-      <c r="O6">
-        <v>2021</v>
-      </c>
-      <c r="P6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q6">
-        <v>60</v>
-      </c>
-      <c r="S6" t="s">
-        <v>90</v>
-      </c>
-      <c r="T6" t="s">
-        <v>91</v>
-      </c>
-      <c r="U6">
-        <v>2022</v>
-      </c>
-      <c r="V6" t="s">
-        <v>97</v>
-      </c>
-      <c r="W6">
-        <v>39</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA6">
-        <v>2023</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7">
-        <v>1091</v>
-      </c>
-      <c r="C7">
-        <v>804</v>
-      </c>
-      <c r="D7">
-        <v>836</v>
-      </c>
-      <c r="E7">
-        <v>836</v>
-      </c>
-      <c r="G7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7">
-        <v>2020</v>
-      </c>
-      <c r="J7" t="s">
-        <v>97</v>
-      </c>
-      <c r="K7">
-        <v>27</v>
-      </c>
-      <c r="M7" t="s">
-        <v>90</v>
-      </c>
-      <c r="N7" t="s">
-        <v>91</v>
-      </c>
-      <c r="O7">
-        <v>2021</v>
-      </c>
-      <c r="P7" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="S7" t="s">
-        <v>90</v>
-      </c>
-      <c r="T7" t="s">
-        <v>91</v>
-      </c>
-      <c r="U7">
-        <v>2022</v>
-      </c>
-      <c r="V7" t="s">
-        <v>99</v>
-      </c>
-      <c r="W7">
-        <v>12</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA7">
-        <v>2023</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC7">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8">
-        <v>1686</v>
-      </c>
-      <c r="C8">
-        <v>1427</v>
-      </c>
-      <c r="D8">
-        <v>1561</v>
-      </c>
-      <c r="E8">
-        <v>1561</v>
-      </c>
-      <c r="G8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8">
-        <v>2020</v>
-      </c>
-      <c r="J8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N8" t="s">
-        <v>91</v>
-      </c>
-      <c r="O8">
-        <v>2021</v>
-      </c>
-      <c r="P8" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q8">
-        <v>6</v>
-      </c>
-      <c r="S8" t="s">
-        <v>90</v>
-      </c>
-      <c r="T8" t="s">
-        <v>91</v>
-      </c>
-      <c r="U8">
-        <v>2022</v>
-      </c>
-      <c r="V8" t="s">
-        <v>101</v>
-      </c>
-      <c r="W8">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA8">
-        <v>2023</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="G9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9">
-        <v>2020</v>
-      </c>
-      <c r="J9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9">
-        <v>6</v>
-      </c>
-      <c r="M9" t="s">
-        <v>90</v>
-      </c>
-      <c r="N9" t="s">
-        <v>91</v>
-      </c>
-      <c r="O9">
-        <v>2021</v>
-      </c>
-      <c r="P9" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q9">
-        <v>52</v>
-      </c>
-      <c r="S9" t="s">
-        <v>90</v>
-      </c>
-      <c r="T9" t="s">
-        <v>91</v>
-      </c>
-      <c r="U9">
-        <v>2022</v>
-      </c>
-      <c r="V9" t="s">
-        <v>102</v>
-      </c>
-      <c r="W9">
-        <v>27</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA9">
-        <v>2023</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" cm="1">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A10" s="87" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="87" cm="1">
         <f t="array" ref="B10:E10">TRANSPOSE('[1]MLS Yearbook 2020-2024'!I62:I65)</f>
         <v>47</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="87">
         <v>30</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="87">
         <v>25</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="87">
         <v>13</v>
       </c>
-      <c r="G10" t="s">
+      <c r="F10" s="87"/>
+      <c r="H10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" t="s">
         <v>90</v>
       </c>
-      <c r="H10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I10">
+      <c r="J10">
         <v>2020</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="N10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" t="s">
+        <v>102</v>
+      </c>
+      <c r="P10">
+        <v>2021</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>103</v>
+      </c>
+      <c r="R10">
+        <v>199</v>
+      </c>
+      <c r="T10" t="s">
+        <v>92</v>
+      </c>
+      <c r="U10" t="s">
+        <v>102</v>
+      </c>
+      <c r="V10">
+        <v>2022</v>
+      </c>
+      <c r="W10" t="s">
+        <v>103</v>
+      </c>
+      <c r="X10">
+        <v>230</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB10">
+        <v>2023</v>
+      </c>
+      <c r="AC10" t="s">
         <v>101</v>
       </c>
-      <c r="K10">
-        <v>2</v>
-      </c>
-      <c r="M10" t="s">
-        <v>93</v>
-      </c>
-      <c r="N10" t="s">
-        <v>104</v>
-      </c>
-      <c r="O10">
-        <v>2021</v>
-      </c>
-      <c r="P10" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10">
-        <v>199</v>
-      </c>
-      <c r="S10" t="s">
-        <v>93</v>
-      </c>
-      <c r="T10" t="s">
-        <v>104</v>
-      </c>
-      <c r="U10">
-        <v>2022</v>
-      </c>
-      <c r="V10" t="s">
-        <v>105</v>
-      </c>
-      <c r="W10">
-        <v>230</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA10">
-        <v>2023</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A11" s="87" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="87">
         <f>B5+B10</f>
         <v>254</v>
       </c>
-      <c r="C11">
-        <f t="shared" ref="C11:E11" si="0">C5+C10</f>
+      <c r="C11" s="87">
+        <f t="shared" ref="C11:E11" si="1">C5+C10</f>
         <v>269</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
+      <c r="D11" s="87">
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="0"/>
+      <c r="E11" s="87">
+        <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F11" s="87"/>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" t="s">
         <v>90</v>
       </c>
-      <c r="H11" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11">
+      <c r="J11">
         <v>2020</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
+        <v>101</v>
+      </c>
+      <c r="L11">
+        <v>32</v>
+      </c>
+      <c r="N11" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11">
+        <v>2021</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>103</v>
+      </c>
+      <c r="R11">
+        <v>8</v>
+      </c>
+      <c r="T11" t="s">
+        <v>92</v>
+      </c>
+      <c r="U11" t="s">
+        <v>104</v>
+      </c>
+      <c r="V11">
+        <v>2022</v>
+      </c>
+      <c r="W11" t="s">
+        <v>103</v>
+      </c>
+      <c r="X11">
+        <v>9</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA11" t="s">
         <v>102</v>
       </c>
-      <c r="K11">
+      <c r="AB11">
+        <v>2023</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD11">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12">
+        <v>2020</v>
+      </c>
+      <c r="K12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12">
+        <v>240</v>
+      </c>
+      <c r="N12" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" t="s">
+        <v>105</v>
+      </c>
+      <c r="P12">
+        <v>2021</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R12">
+        <v>38</v>
+      </c>
+      <c r="T12" t="s">
+        <v>95</v>
+      </c>
+      <c r="U12" t="s">
+        <v>105</v>
+      </c>
+      <c r="V12">
+        <v>2022</v>
+      </c>
+      <c r="W12" t="s">
+        <v>106</v>
+      </c>
+      <c r="X12">
+        <v>45</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB12">
+        <v>2023</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13">
+        <v>2020</v>
+      </c>
+      <c r="K13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13">
+        <v>10</v>
+      </c>
+      <c r="N13" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" t="s">
+        <v>107</v>
+      </c>
+      <c r="P13">
+        <v>2021</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>106</v>
+      </c>
+      <c r="R13">
+        <v>211</v>
+      </c>
+      <c r="T13" t="s">
+        <v>95</v>
+      </c>
+      <c r="U13" t="s">
+        <v>107</v>
+      </c>
+      <c r="V13">
+        <v>2022</v>
+      </c>
+      <c r="W13" t="s">
+        <v>106</v>
+      </c>
+      <c r="X13">
+        <v>239</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB13">
+        <v>2023</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD13">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14">
+        <v>2020</v>
+      </c>
+      <c r="K14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14">
         <v>32</v>
       </c>
-      <c r="M11" t="s">
-        <v>93</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="N14" t="s">
+        <v>97</v>
+      </c>
+      <c r="O14" t="s">
+        <v>109</v>
+      </c>
+      <c r="P14">
+        <v>2021</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>110</v>
+      </c>
+      <c r="R14">
+        <v>95</v>
+      </c>
+      <c r="T14" t="s">
+        <v>97</v>
+      </c>
+      <c r="U14" t="s">
+        <v>109</v>
+      </c>
+      <c r="V14">
+        <v>2022</v>
+      </c>
+      <c r="W14" t="s">
+        <v>110</v>
+      </c>
+      <c r="X14">
+        <v>95</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA14" t="s">
         <v>107</v>
       </c>
-      <c r="O11">
+      <c r="AB14">
+        <v>2023</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD14">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15">
+        <v>2020</v>
+      </c>
+      <c r="K15" t="s">
+        <v>106</v>
+      </c>
+      <c r="L15">
+        <v>302</v>
+      </c>
+      <c r="N15" t="s">
+        <v>97</v>
+      </c>
+      <c r="O15" t="s">
+        <v>111</v>
+      </c>
+      <c r="P15">
         <v>2021</v>
       </c>
-      <c r="P11" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q11">
-        <v>8</v>
-      </c>
-      <c r="S11" t="s">
-        <v>93</v>
-      </c>
-      <c r="T11" t="s">
-        <v>107</v>
-      </c>
-      <c r="U11">
+      <c r="Q15" t="s">
+        <v>110</v>
+      </c>
+      <c r="R15">
+        <v>180</v>
+      </c>
+      <c r="T15" t="s">
+        <v>97</v>
+      </c>
+      <c r="U15" t="s">
+        <v>111</v>
+      </c>
+      <c r="V15">
         <v>2022</v>
       </c>
-      <c r="V11" t="s">
-        <v>105</v>
-      </c>
-      <c r="W11">
-        <v>9</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA11">
+      <c r="W15" t="s">
+        <v>110</v>
+      </c>
+      <c r="X15">
+        <v>140</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB15">
         <v>2023</v>
       </c>
-      <c r="AB11" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC11">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="G12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12">
-        <v>2020</v>
-      </c>
-      <c r="J12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K12">
-        <v>240</v>
-      </c>
-      <c r="M12" t="s">
-        <v>96</v>
-      </c>
-      <c r="N12" t="s">
-        <v>108</v>
-      </c>
-      <c r="O12">
-        <v>2021</v>
-      </c>
-      <c r="P12" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q12">
-        <v>38</v>
-      </c>
-      <c r="S12" t="s">
-        <v>96</v>
-      </c>
-      <c r="T12" t="s">
-        <v>108</v>
-      </c>
-      <c r="U12">
-        <v>2022</v>
-      </c>
-      <c r="V12" t="s">
-        <v>109</v>
-      </c>
-      <c r="W12">
-        <v>45</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA12">
-        <v>2023</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="G13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13">
-        <v>2020</v>
-      </c>
-      <c r="J13" t="s">
-        <v>105</v>
-      </c>
-      <c r="K13">
-        <v>10</v>
-      </c>
-      <c r="M13" t="s">
-        <v>96</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="AC15" t="s">
         <v>110</v>
       </c>
-      <c r="O13">
-        <v>2021</v>
-      </c>
-      <c r="P13" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q13">
-        <v>211</v>
-      </c>
-      <c r="S13" t="s">
-        <v>96</v>
-      </c>
-      <c r="T13" t="s">
-        <v>110</v>
-      </c>
-      <c r="U13">
-        <v>2022</v>
-      </c>
-      <c r="V13" t="s">
-        <v>109</v>
-      </c>
-      <c r="W13">
-        <v>239</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA13">
-        <v>2023</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC13">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14">
-        <v>2020</v>
-      </c>
-      <c r="J14" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14">
-        <v>32</v>
-      </c>
-      <c r="M14" t="s">
-        <v>98</v>
-      </c>
-      <c r="N14" t="s">
-        <v>112</v>
-      </c>
-      <c r="O14">
-        <v>2021</v>
-      </c>
-      <c r="P14" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q14">
-        <v>95</v>
-      </c>
-      <c r="S14" t="s">
-        <v>98</v>
-      </c>
-      <c r="T14" t="s">
-        <v>112</v>
-      </c>
-      <c r="U14">
-        <v>2022</v>
-      </c>
-      <c r="V14" t="s">
-        <v>113</v>
-      </c>
-      <c r="W14">
-        <v>95</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA14">
-        <v>2023</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC14">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
+      <c r="AD15">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
         <v>84</v>
-      </c>
-      <c r="G15" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" t="s">
-        <v>110</v>
-      </c>
-      <c r="I15">
-        <v>2020</v>
-      </c>
-      <c r="J15" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15">
-        <v>302</v>
-      </c>
-      <c r="M15" t="s">
-        <v>98</v>
-      </c>
-      <c r="N15" t="s">
-        <v>114</v>
-      </c>
-      <c r="O15">
-        <v>2021</v>
-      </c>
-      <c r="P15" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15">
-        <v>180</v>
-      </c>
-      <c r="S15" t="s">
-        <v>98</v>
-      </c>
-      <c r="T15" t="s">
-        <v>114</v>
-      </c>
-      <c r="U15">
-        <v>2022</v>
-      </c>
-      <c r="V15" t="s">
-        <v>113</v>
-      </c>
-      <c r="W15">
-        <v>140</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA15">
-        <v>2023</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC15">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>85</v>
       </c>
       <c r="B16">
         <v>2020</v>
@@ -3098,345 +3459,348 @@
       <c r="E16">
         <v>2023</v>
       </c>
-      <c r="G16" t="s">
-        <v>98</v>
-      </c>
       <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16">
+        <v>2020</v>
+      </c>
+      <c r="K16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16">
+        <v>155</v>
+      </c>
+      <c r="N16" t="s">
+        <v>97</v>
+      </c>
+      <c r="O16" t="s">
         <v>112</v>
       </c>
-      <c r="I16">
+      <c r="P16">
+        <v>2021</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>110</v>
+      </c>
+      <c r="R16">
+        <v>708</v>
+      </c>
+      <c r="T16" t="s">
+        <v>97</v>
+      </c>
+      <c r="U16" t="s">
+        <v>112</v>
+      </c>
+      <c r="V16">
+        <v>2022</v>
+      </c>
+      <c r="W16" t="s">
+        <v>110</v>
+      </c>
+      <c r="X16">
+        <v>461</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB16">
+        <v>2023</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17">
+        <f>SUM(L4:L11)</f>
+        <v>120</v>
+      </c>
+      <c r="C17">
+        <f>SUM(R4:R9)</f>
+        <v>139</v>
+      </c>
+      <c r="D17">
+        <f>SUM(X4:X9)</f>
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <f>SUM(AD4:AD10)</f>
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
+        <v>111</v>
+      </c>
+      <c r="J17">
         <v>2020</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K17" t="s">
+        <v>110</v>
+      </c>
+      <c r="L17">
+        <v>181</v>
+      </c>
+      <c r="N17" t="s">
+        <v>97</v>
+      </c>
+      <c r="O17" t="s">
         <v>113</v>
       </c>
-      <c r="K16">
-        <v>155</v>
-      </c>
-      <c r="M16" t="s">
-        <v>98</v>
-      </c>
-      <c r="N16" t="s">
-        <v>115</v>
-      </c>
-      <c r="O16">
+      <c r="P17">
         <v>2021</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q17" t="s">
+        <v>110</v>
+      </c>
+      <c r="R17">
+        <v>108</v>
+      </c>
+      <c r="T17" t="s">
+        <v>97</v>
+      </c>
+      <c r="U17" t="s">
         <v>113</v>
       </c>
-      <c r="Q16">
-        <v>708</v>
-      </c>
-      <c r="S16" t="s">
-        <v>98</v>
-      </c>
-      <c r="T16" t="s">
-        <v>115</v>
-      </c>
-      <c r="U16">
+      <c r="V17">
         <v>2022</v>
       </c>
-      <c r="V16" t="s">
+      <c r="W17" t="s">
+        <v>110</v>
+      </c>
+      <c r="X17">
+        <v>108</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB17">
+        <v>2023</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD17">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18">
+        <f>SUM(L12:L13)</f>
+        <v>250</v>
+      </c>
+      <c r="C18">
+        <f>SUM(R10:R11)</f>
+        <v>207</v>
+      </c>
+      <c r="D18">
+        <f>SUM(X10:X11)</f>
+        <v>239</v>
+      </c>
+      <c r="E18">
+        <f>SUM(AD11:AD12)</f>
+        <v>175</v>
+      </c>
+      <c r="H18" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" t="s">
+        <v>112</v>
+      </c>
+      <c r="J18">
+        <v>2020</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18">
+        <v>896</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA18" t="s">
         <v>113</v>
       </c>
-      <c r="W16">
+      <c r="AB18">
+        <v>2023</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>110</v>
+      </c>
+      <c r="AD18">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19">
+        <f>SUM(L14:L15)</f>
+        <v>334</v>
+      </c>
+      <c r="C19">
+        <f>SUM(R12:R13)</f>
+        <v>249</v>
+      </c>
+      <c r="D19">
+        <f>SUM(X12:X13)</f>
+        <v>284</v>
+      </c>
+      <c r="E19">
+        <f>SUM(AD13:AD14)</f>
         <v>461</v>
       </c>
-      <c r="Y16" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA16">
-        <v>2023</v>
-      </c>
-      <c r="AB16" t="s">
+      <c r="H19" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" t="s">
         <v>113</v>
       </c>
-      <c r="AC16">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17">
-        <f>SUM(K4:K11)</f>
-        <v>120</v>
-      </c>
-      <c r="C17">
-        <f>SUM(Q4:Q9)</f>
-        <v>139</v>
-      </c>
-      <c r="D17">
-        <f>SUM(W4:W9)</f>
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <f>SUM(AC4:AC10)</f>
-        <v>89</v>
-      </c>
-      <c r="G17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H17" t="s">
-        <v>114</v>
-      </c>
-      <c r="I17">
+      <c r="J19">
         <v>2020</v>
       </c>
-      <c r="J17" t="s">
-        <v>113</v>
-      </c>
-      <c r="K17">
-        <v>181</v>
-      </c>
-      <c r="M17" t="s">
-        <v>98</v>
-      </c>
-      <c r="N17" t="s">
-        <v>116</v>
-      </c>
-      <c r="O17">
-        <v>2021</v>
-      </c>
-      <c r="P17" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q17">
-        <v>108</v>
-      </c>
-      <c r="S17" t="s">
-        <v>98</v>
-      </c>
-      <c r="T17" t="s">
-        <v>116</v>
-      </c>
-      <c r="U17">
-        <v>2022</v>
-      </c>
-      <c r="V17" t="s">
-        <v>113</v>
-      </c>
-      <c r="W17">
-        <v>108</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA17">
-        <v>2023</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC17">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18">
-        <f>SUM(K12:K13)</f>
-        <v>250</v>
-      </c>
-      <c r="C18">
-        <f>SUM(Q10:Q11)</f>
-        <v>207</v>
-      </c>
-      <c r="D18">
-        <f>SUM(W10:W11)</f>
-        <v>239</v>
-      </c>
-      <c r="E18">
-        <f>SUM(AC11:AC12)</f>
-        <v>175</v>
-      </c>
-      <c r="G18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18">
-        <v>2020</v>
-      </c>
-      <c r="J18" t="s">
-        <v>113</v>
-      </c>
-      <c r="K18">
-        <v>896</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA18">
-        <v>2023</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC18">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19">
-        <f>SUM(K14:K15)</f>
-        <v>334</v>
-      </c>
-      <c r="C19">
-        <f>SUM(Q12:Q13)</f>
-        <v>249</v>
-      </c>
-      <c r="D19">
-        <f>SUM(W12:W13)</f>
-        <v>284</v>
-      </c>
-      <c r="E19">
-        <f>SUM(AC13:AC14)</f>
-        <v>461</v>
-      </c>
-      <c r="G19" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" t="s">
-        <v>116</v>
-      </c>
-      <c r="I19">
-        <v>2020</v>
-      </c>
-      <c r="J19" t="s">
-        <v>113</v>
-      </c>
-      <c r="K19">
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B20">
-        <f>SUM(K16:K19)</f>
+        <f>SUM(L16:L19)</f>
         <v>1326</v>
       </c>
       <c r="C20">
-        <f>SUM(Q14:Q17)</f>
+        <f>SUM(R14:R17)</f>
         <v>1091</v>
       </c>
       <c r="D20">
-        <f>SUM(W14:W17)</f>
+        <f>SUM(X14:X17)</f>
         <v>804</v>
       </c>
       <c r="E20">
-        <f>SUM(AC15:AC18)</f>
+        <f>SUM(AD15:AD18)</f>
         <v>836</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21">
         <f>SUM(B17:B20)</f>
         <v>2030</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:E21" si="1">SUM(C17:C20)</f>
+        <f t="shared" ref="C21:E21" si="2">SUM(C17:C20)</f>
         <v>1686</v>
       </c>
       <c r="D21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1427</v>
       </c>
       <c r="E21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1561</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.4">
       <c r="B24">
-        <f>SUM(K4:K19)</f>
+        <f>SUM(L4:L19)</f>
         <v>2030</v>
       </c>
       <c r="C24">
-        <f>SUM(Q4:Q17)</f>
+        <f>SUM(R4:R17)</f>
         <v>1686</v>
       </c>
       <c r="D24">
-        <f>SUM(W4:W17)</f>
+        <f>SUM(X4:X17)</f>
         <v>1427</v>
       </c>
       <c r="E24">
-        <f>SUM(AC4:AC18)</f>
+        <f>SUM(AD4:AD18)</f>
         <v>1561</v>
       </c>
     </row>
-    <row r="64" spans="9:11" x14ac:dyDescent="0.4">
-      <c r="I64">
+    <row r="64" spans="10:12" x14ac:dyDescent="0.4">
+      <c r="J64">
         <v>2020</v>
       </c>
-      <c r="J64" t="s">
-        <v>105</v>
-      </c>
-      <c r="K64">
+      <c r="K64" t="s">
+        <v>103</v>
+      </c>
+      <c r="L64">
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="9:11" x14ac:dyDescent="0.4">
-      <c r="I65">
+    <row r="65" spans="10:12" x14ac:dyDescent="0.4">
+      <c r="J65">
         <v>2021</v>
       </c>
-      <c r="J65" t="s">
-        <v>105</v>
-      </c>
-      <c r="K65">
+      <c r="K65" t="s">
+        <v>103</v>
+      </c>
+      <c r="L65">
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="9:11" x14ac:dyDescent="0.4">
-      <c r="I66">
+    <row r="66" spans="10:12" x14ac:dyDescent="0.4">
+      <c r="J66">
         <v>2022</v>
       </c>
-      <c r="J66" t="s">
-        <v>105</v>
-      </c>
-      <c r="K66">
+      <c r="K66" t="s">
+        <v>103</v>
+      </c>
+      <c r="L66">
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="9:11" x14ac:dyDescent="0.4">
-      <c r="I67">
+    <row r="67" spans="10:12" x14ac:dyDescent="0.4">
+      <c r="J67">
         <v>2023</v>
       </c>
-      <c r="J67" t="s">
-        <v>105</v>
-      </c>
-      <c r="K67">
+      <c r="K67" t="s">
+        <v>103</v>
+      </c>
+      <c r="L67">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3458,13 +3822,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.4">
